--- a/AAII_Financials/Quarterly/E_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/E_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>E</t>
   </si>
@@ -656,503 +656,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25897400</v>
+      </c>
+      <c r="E8" s="3">
         <v>24623700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24106500</v>
       </c>
-      <c r="F8" s="3">
-        <v>22456800</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
         <v>24820600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24768600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23439700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24704800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24996200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27577100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23973300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21628800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29745800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>76232800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>40312300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69295600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34959600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>49637700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20483700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32573700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15334700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21899900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10717400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24032700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15134200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>38409000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20440200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>43503300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>21810500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>47021500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>21814200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>39606000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>19689300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>37282600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>17597300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>37799800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>20248600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>34042800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>15488400</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20189600</v>
+      </c>
+      <c r="E9" s="3">
         <v>20401500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19373500</v>
       </c>
-      <c r="F9" s="3">
-        <v>17738100</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3">
         <v>19195800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20197700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18774300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18308200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18730200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21516500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17934000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16518600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23876600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>50463400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29605800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>42773200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25547500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27416900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14869800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16600000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10855100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10602400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7816400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11638900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12729800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18881700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14924100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23405700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15782600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>25931500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15338000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>20865300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14089500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19400300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>13535700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>20623300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>15280400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>16698600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>12158300</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5707800</v>
+      </c>
+      <c r="E10" s="3">
         <v>4222100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4733100</v>
       </c>
-      <c r="F10" s="3">
-        <v>4718700</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3">
         <v>5624700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4570900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4665400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6396700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6266000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6060600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6039400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5110300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5869200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25769400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10706500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26522400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9412100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22220800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5613900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>15973700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4479600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11297500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2900900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12393800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2404400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19527300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5516100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>20097600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6027900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21089900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6476100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>18740700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5599800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>17882300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4061600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>17176500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4968200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>17344200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3330100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,16 +1206,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E12" s="3">
         <v>243000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1211,11 +1224,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>184300</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1223,11 +1236,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>183500</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,246 +1448,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1424700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-425000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>153700</v>
       </c>
-      <c r="F14" s="3">
-        <v>319400</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>301600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1070500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>37900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1469000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-39900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>305100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-83600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>319900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>29300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1732300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>155600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-115300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-227400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>64000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>177700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>726800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>73000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>499700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>13500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3418900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>524700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2358200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>42900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>581100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>90600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1141500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>237000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>141600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>38400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-425200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-136900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>285000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>184000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-272300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>86900</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2042700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3413200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2171800</v>
       </c>
-      <c r="F15" s="3">
-        <v>2140900</v>
-      </c>
       <c r="G15" s="3">
+        <v>1884900</v>
+      </c>
+      <c r="H15" s="3">
         <v>2024400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4642300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2120200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2146100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2144800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3712800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1959100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2146300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2029600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4225500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1857700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3688700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2007500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4055600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1915800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3514700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1798600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3438000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1844300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4207600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2050900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4996500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2532100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4500900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2196300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>4001800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1887400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3960500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2014800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4159200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>2174400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4238900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>2056600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>4525000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>2217300</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23137200</v>
+      </c>
+      <c r="E17" s="3">
         <v>25071000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22313700</v>
       </c>
-      <c r="F17" s="3">
-        <v>20712900</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3">
         <v>22013600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>26130000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21820200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21416500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21972200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26729300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20608600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19316600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26931800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>69324700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33154800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56503900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28774800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40439100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17475900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28493000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13364700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21401200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10489000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28150900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16328700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>36426700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18140900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>37911800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18848300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>41138900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17981900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>34080800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17055200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>31110500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>16293500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>34799600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>17880000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>32082600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>15263100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2760200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-447300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1792800</v>
       </c>
-      <c r="F18" s="3">
-        <v>1744000</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3">
         <v>2807000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1361400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1619500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3288300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3024100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>847800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3364700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2312200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2814000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6908100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7157500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12791700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6184800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9198600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3007800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4080700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1970000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>498700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>228300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4118200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1194500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1982300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2299300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5591400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2962200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5882600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3832300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5525100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2634100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6172100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1303800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3000200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2368500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1960300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,603 +2023,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1160700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-288800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-421200</v>
       </c>
-      <c r="F20" s="3">
-        <v>-355800</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>-374000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>156300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-375000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-281600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-505100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-377900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-363500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-389000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4417100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2896300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1107700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>217600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-341500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-39800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-496200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-106900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-336100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-225200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1527300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>297700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>185900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-163500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>729800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-175000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>186700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-171300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-699000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-169400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>48200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-120100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-599800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-529400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5963700</v>
+      </c>
+      <c r="E21" s="3">
         <v>3254700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4385800</v>
       </c>
-      <c r="F21" s="3">
-        <v>4240800</v>
-      </c>
       <c r="G21" s="3">
+        <v>1884900</v>
+      </c>
+      <c r="H21" s="3">
         <v>5205400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3124500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3940400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5809500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5450400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5065800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5701700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4822100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5232500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15550700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11911500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17588000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8409900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12912700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4883700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7099200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3661700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3600600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1847500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1437800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-559600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7276500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4778700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10278200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4995000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10613000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5544600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9671200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4477600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9631200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3308700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7286200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4305100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5720000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-1096800</v>
+      </c>
+      <c r="E22" s="3">
         <v>-6711300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1349300</v>
       </c>
-      <c r="F22" s="3">
-        <v>3904900</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
         <v>2688100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>-4327600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2290900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1725100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1968900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>-5121000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2250200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1496700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2369600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>530500</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>512500</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>479200</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>456000</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>459800</v>
       </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>550900</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>642100</v>
       </c>
-      <c r="AC22" s="3" t="s">
+      <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>668200</v>
       </c>
-      <c r="AE22" s="3" t="s">
+      <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>442400</v>
       </c>
-      <c r="AG22" s="3" t="s">
+      <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>341500</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>415100</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>427500</v>
       </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AN22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>448400</v>
       </c>
-      <c r="AO22" s="3" t="s">
+      <c r="AP22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4551600</v>
+      </c>
+      <c r="E23" s="3">
         <v>349900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1930100</v>
       </c>
-      <c r="F23" s="3">
-        <v>1650000</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3">
         <v>2626500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1838100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2220100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2939900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1273400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3638900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2245600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3890700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10794700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10053800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13386900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6402400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8377900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2967900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3128500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1863100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-297200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6196400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2610500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1637900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2246600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5109100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2798700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6170000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3657300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5370300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2462800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5057900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1134300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2621000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2248500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>912100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-304000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1498900</v>
+      </c>
+      <c r="E24" s="3">
         <v>189000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>915200</v>
       </c>
-      <c r="F24" s="3">
-        <v>991200</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3">
         <v>1334800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-252600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1231300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1475400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1605400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1047900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1590800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1902800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1275500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3536600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3696000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5326200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2497200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3252300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1667000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1952000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>953300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>995400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>523100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1802200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>582500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3231400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1604700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3321000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1510500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3884600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1962700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2949200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1421900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2374100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>747200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1515800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1163500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1170300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>354500</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3052700</v>
+      </c>
+      <c r="E26" s="3">
         <v>160900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1014900</v>
       </c>
-      <c r="F26" s="3">
-        <v>658800</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3">
         <v>1291600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>298200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>606700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>744700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1334600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>225500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2048100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>342800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2615200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7258100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6357800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8060600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3905200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5125600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1300900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1176500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>909900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1292600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-520000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7998600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3193100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1593500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>641900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1788100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1288200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2285400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1694600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2421100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1040900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2683800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>387100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1105200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1085000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-258200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-658500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3659300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-172600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>942200</v>
       </c>
-      <c r="F27" s="3">
-        <v>637700</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3">
         <v>1266800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>101500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>582200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>708200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1306500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>70700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2027900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>321000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2594500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7187200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6335100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8049800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3898700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5114800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1295500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1167000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>905600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1296600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-522100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8001800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3195300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>640700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1783400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1284600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2280600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1693500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2413400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1038700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2682700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>386000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1102900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1082700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-260600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-659700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,13 +3119,16 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>129100</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -3163,8 +3223,8 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
+      <c r="AJ29" s="3">
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3175,14 +3235,17 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3485,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1160700</v>
+      </c>
+      <c r="E32" s="3">
         <v>288800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>421200</v>
       </c>
-      <c r="F32" s="3">
-        <v>355800</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>374000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-156300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>375000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>281600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>505100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>377900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>363500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>389000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4417100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2896300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1107700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-217600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>341500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>39800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>496200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>106900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>336100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>225200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1527300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1416000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-297700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>52700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-185900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>163500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-729800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>175000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-186700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>171300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>699000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>169400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-48200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>120100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>599800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>529400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3791800</v>
+      </c>
+      <c r="E33" s="3">
         <v>105700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>942200</v>
       </c>
-      <c r="F33" s="3">
-        <v>637700</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3">
         <v>1266800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>238100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>582200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>708200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1306500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>191200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2027900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>321000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2594500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7187200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6335100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8049800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3898700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5114800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1295500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1167000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>905600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1296600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-522100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8001800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3195300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>640700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1783400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1284600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2280600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1693500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2413400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1038700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2682700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>386000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1102900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1082700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-260600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-659700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3791800</v>
+      </c>
+      <c r="E35" s="3">
         <v>105700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>942200</v>
       </c>
-      <c r="F35" s="3">
-        <v>637700</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3">
         <v>1266800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>238100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>582200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>708200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1306500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>191200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2027900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>321000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2594500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7187200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6335100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8049800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3898700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5114800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1295500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1167000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>905600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1296600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-522100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8001800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3195300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>640700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1783400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1284600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2280600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1693500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2413400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1038700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2682700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>386000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1102900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1082700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-260600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-659700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,1079 +4190,1107 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9556700</v>
+      </c>
+      <c r="E41" s="3">
         <v>9510400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10476400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10765700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9886500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8471900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10447200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10907500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9475700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11266700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10117500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12464000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11023500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11247700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12406400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11860300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14650200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8948200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7930300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10276400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8950700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9388500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7139700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7120400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3972000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6997500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5430400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12415700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12062800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12817900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11438200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8159200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6286100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8261200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6578200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5541500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6131700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6660200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5636600</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7680800</v>
+      </c>
+      <c r="E42" s="3">
         <v>8208300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8001900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8052800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7608100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7037000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7297600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7772400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7987900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7496400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8355200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9042600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8477800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9138800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7296900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>6859400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6840900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6830900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6961100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6778600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6515200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5487700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5823700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>6591300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7202200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7891700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>8309100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7846600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7852500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7750400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7203800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7120500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>7029400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>6977700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>7141500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>7074100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>7192000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>7517100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>7419700</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21653100</v>
+      </c>
+      <c r="E43" s="3">
         <v>20669200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16148100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17977700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19767600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20220500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17009800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18751700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19634300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20804700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17384600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18562200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20963700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25993200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3045400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24567100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1928100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25796200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1279400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15547300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14600400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11783300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11820600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13183600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>15358900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>16594700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17691300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>17718900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21203400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17924500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>18025100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>17884200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19282000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>18689000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>18287300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>18593600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>22792100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>21909200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>23094700</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7319800</v>
+      </c>
+      <c r="E44" s="3">
         <v>6038500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7344800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6809200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6088400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6480000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7344400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7156300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6778500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6837600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7285100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6631000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7010000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8538500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10978800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9597000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7564500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6582700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6082300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4859400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4670000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3882900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4183800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4536000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4148700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5526500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5731700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5375000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5446700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5501700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5615500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5181500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4749900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5184700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5203800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5450600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>5304800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>5443000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>5350200</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24282000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12949400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6574000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7755700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2759400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3346100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7638900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9659300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7527200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5219400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7732900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6453100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8443100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13306700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34419200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27240600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24697700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14301400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21094300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7490600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3147600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2230200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2566700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3357800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4698500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3742700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2390000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3563300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2976300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2671000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4842400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3403800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2035700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1764900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1417100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1606700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1574200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3041300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2486100</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70492400</v>
+      </c>
+      <c r="E46" s="3">
         <v>57375800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>48545100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>51361100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46110000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45555400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>49737900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>54247300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51403600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>51624800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>50875300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>53152800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>55918100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68224800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>91520200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>80124400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>81789200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>62459300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>59126100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>44952300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37883800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>32772600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>31534500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34789100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>35380400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>40753100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>39552500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>46919500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>49541700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>46665400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>47125100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>41749300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>39383100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>40877500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>38627900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>38266600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>42994700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>44570700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>43987400</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21974200</v>
+      </c>
+      <c r="E47" s="3">
         <v>17080000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17110200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16770400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16479700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16158000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15552100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15653100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15942400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15416200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15601200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15659400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14767500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>19505900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16904300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11906000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11482700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11061100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9293600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>10190700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9870100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>10093700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9878700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>11498200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>11361800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>14221400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14122900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10932300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>9954700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>11838500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7096400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7821100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6682400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>6904700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7165000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7816900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>6947400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>8287100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>6394900</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>61822200</v>
+      </c>
+      <c r="E48" s="3">
         <v>65422100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>68971000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68332400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65835500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>68005000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68836700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>67442400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70004300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67572700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66273300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67163800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>66233200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>67317700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69024300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>64493900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>67783200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>66260200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64550500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>62007300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>64192000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>58433700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>62975600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>69722200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>73767300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>78848000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>84850200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>78722300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>79288200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>71331200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>66202400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>65516600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>68504200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>70862600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>73306300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>75829700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>79328100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>83097500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>79680600</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1750300</v>
+      </c>
+      <c r="E49" s="3">
         <v>7070600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7063200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7540800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6969300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6661100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7191600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6937700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6912300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7051000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5748300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6003300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5967000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6119500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5473700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5278400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5291400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5202600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4010400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3595100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3297800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2928400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3139600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3366500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3498500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3571100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3906500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3710400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3741000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3749800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3374900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3285200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3247900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3281800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3316600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3414200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3659900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3837200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3327800</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4958300</v>
+      </c>
+      <c r="E52" s="3">
         <v>6101900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9523600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8829100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14163400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9201800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9182500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8864200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8780900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11009200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7099900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6395200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6546100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7331200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9548000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15967900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7098800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4367800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8290000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6203100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7097100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5134600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6746400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6171300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6907600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6711400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7440600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6627800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7820700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6438500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12644400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11569600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7710200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7021400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7602600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>6865500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7546500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>6399600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>7452500</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>167948100</v>
+      </c>
+      <c r="E54" s="3">
         <v>160935800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>158378500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>159964800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>156136000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>152126500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>155435000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>157798100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>158088300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>157627900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>149231600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>153296900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>154135200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>168499200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>192470500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>177770500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>173445300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>149351000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>145270600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>126948400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>122340800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>109362900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114274900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>125547400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>130915700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>144105100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>149872600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>146912400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>150346300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>140023400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>136443000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>129941700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>125527800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>128948100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>130018400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>132192900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>140476500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>146192200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>140843100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +5986,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16980500</v>
+      </c>
+      <c r="E57" s="3">
         <v>16321500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13890600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14536700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15207500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15705600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12480500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13558300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13731800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15730100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12189900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12141900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14518700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>21628100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26408000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17629400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26126400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>18207500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17245500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10683700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14551700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8656400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12510800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8665100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15030600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12234500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17631300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12562800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>19489400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13774900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>18347400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11548800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>16726900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>12218500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>17893500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>10525400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>19144500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>12956500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>17115300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10059400</v>
+      </c>
+      <c r="E58" s="3">
         <v>11302100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12377100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12246600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11605100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10455500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10427200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10163900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10256800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8998600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6278600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8239100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7931300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9333700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9062800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7111800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8464300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5450900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6122200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6938400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5867700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5625300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5257000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6066600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6027300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7584700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7484700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8486500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8877100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6840700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6823900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5439500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4143900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>5080400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>7975100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>7901100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7921200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>7835200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5509900</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17604200</v>
+      </c>
+      <c r="E59" s="3">
         <v>12674700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13939900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10752800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13500900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10990800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15290000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14088700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17165800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14746300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17057600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13564400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18170400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22997100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42609800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40062800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32085900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23122800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24804200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15447900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6795500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9347600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6659200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13200000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9732000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14787600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8180500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14916800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9251200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12957500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8418900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12707200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6317900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10453600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4511500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10654400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4990600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>11718100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5063800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47645400</v>
+      </c>
+      <c r="E60" s="3">
         <v>42614800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40207700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40934800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40313400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39364300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38197600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>41199000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41154400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41915600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35526000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>36907200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40620400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>53958900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>78080600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>64804000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>66676600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>46781100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>48171900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>33069900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27214900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23629400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24427000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27931700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30789800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34606700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>33296500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35966100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>37617700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33573100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33590200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29695400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>27188700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>27752400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30380100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>29080900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>32056400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>32509800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>27689000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32200400</v>
+      </c>
+      <c r="E61" s="3">
         <v>28855200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28308100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28702300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27093600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27688200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28986200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29573600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29032300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28654800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27634400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28292600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26568900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25963300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25954100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28384200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29921700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30466500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>27718300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>26875300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28299400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>25996200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28675100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29966200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26733800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27631400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29195200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28007700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28305400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>23755000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>22013600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20902600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>21810700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>22640600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>22888600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>22476800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>22692200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>24138200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>26862600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16993000</v>
+      </c>
+      <c r="E62" s="3">
         <v>20535400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20856500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20015300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20158900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20300200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22055500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20652500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22282900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20974900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20083600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19787100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20004300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27404200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25922800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27988100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25199300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23840400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>26002800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24069500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24551900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22341800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>23255200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25279700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>23881100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25948000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24329500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>22935100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>22337500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>22281100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>24497900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>23926500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>23569700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>24610900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>24490800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>25737300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>26113200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>27231200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>27431900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>102907600</v>
+      </c>
+      <c r="E66" s="3">
         <v>98957400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>96233700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>97246000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>94236900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>94513900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>95789600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>98632800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98633100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>98333100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>88600800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>92676900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>93777700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>107848100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>130480500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>121279600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>121906400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>101176900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>101987800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>84103600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>80153000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>72045200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>76433000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>83256100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>81522600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>88257400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>86892200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>86976000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>88331200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>79676600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>80161400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>74582700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>72625000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>75058900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>77813400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>77348900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>80920200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>83936800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>82039900</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7492,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>44228300</v>
+      </c>
+      <c r="E72" s="3">
         <v>43179500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>42960200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>44749300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>40307000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>37410700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>40731700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>41029700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40993600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>42796500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40919800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>42652800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41541700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>42632600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>45918900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38480700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40170500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37851400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33386100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33746000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>32824500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29607800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28680300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>30425500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>37599300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>42958400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>48769300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>47823000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>49154700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>47950000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>51929800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>44052900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>48990600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>43912400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>48292700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>42899300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>55760700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>45346600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>54913200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59409300</v>
+      </c>
+      <c r="E76" s="3">
         <v>56287400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57776600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>58412200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>57880500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>54648500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>56922800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58242800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58522000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58786300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60168300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60160500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>59845700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>60651100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>61990000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56490900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>51538900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>48174200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>43282800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>42844800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>42187800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>37317700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>37841800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>42291300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>49393100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>55847700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>62980400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>59936400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>62015100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>60346800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>56281600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>55359000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>52902700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>53889200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>52205100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>54844000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>59556400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>62255400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>58803200</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3791800</v>
+      </c>
+      <c r="E81" s="3">
         <v>105700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>942200</v>
       </c>
-      <c r="F81" s="3">
-        <v>637700</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3">
         <v>1266800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>238100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>582200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>708200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1306500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>191200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2027900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>321000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2594500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7187200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6335100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8049800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3898700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5114800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1295500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1167000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>905600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1296600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-522100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8001800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3195300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>640700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1783400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1284600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2280600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1693500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2413400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1038700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2682700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>386000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1102900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1082700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-260600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-659700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2024400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1244400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2054400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2065800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2112400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1581700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1872400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2027300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2012200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1709900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1685600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1615100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2049500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4225500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1857700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3688700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2007500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4055600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1915800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3514700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1798600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3438000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1844300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4207600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2050900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4996500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2532100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4500900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2196300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4000600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1887400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3959400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2014800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4158100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2174400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4237800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>2056600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>4350100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2256100</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4878300</v>
+      </c>
+      <c r="E89" s="3">
         <v>5107400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3611400</v>
       </c>
-      <c r="F89" s="3">
-        <v>4130400</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>2577800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3747800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3342600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4897700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2054200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4614800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3724600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4850400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3239900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11274300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6036800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7922500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3370900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9505400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3158500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4330400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1455800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2436600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1511200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2595300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1063600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6740600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2510000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7777200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2465700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>9968300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4543400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5731600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2401300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>6147400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2424600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5211600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2173300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5363100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1555300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9661,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2415200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3444900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2418200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-2373500</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1822300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2478500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2101300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2036900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1963500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2632900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1911500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2715100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2242500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2767000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2099000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1829000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1364000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1647000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1156400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1933000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-870800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2693500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1668000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>4778200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2249100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4833800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2563400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5195300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1940500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4815800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2752700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4144600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1740200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-5381100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3059700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>678500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-4815000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3208000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3956800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1786900</v>
       </c>
-      <c r="F94" s="3">
-        <v>-2626000</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2344400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2585200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1801200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2347600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3791100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2794300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1910500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3551300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1932900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5967700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2618500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1773600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>620200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8552500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2610400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4372700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2154100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1841200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-845900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2990200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2871300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8268800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5862800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5093800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2658700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5675600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1949400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3006300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3201800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>500400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-602500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4728100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2563700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5304400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2421600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,109 +10193,110 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1076200</v>
+      </c>
+      <c r="E96" s="3">
         <v>1150600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>916300</v>
       </c>
-      <c r="F96" s="3">
-        <v>952400</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>884100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>874800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>868800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>815400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>885700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>882100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>836200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>864600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>873500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1649200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-811600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1653900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-32600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1646700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1627200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-887700</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-429900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-439000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1673500</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1801300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1890200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1735200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1790900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1672500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1581100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-1615700</v>
       </c>
       <c r="AK96" s="3">
         <v>-1615700</v>
@@ -10072,16 +10305,19 @@
         <v>-1615700</v>
       </c>
       <c r="AM96" s="3">
-        <v>0</v>
+        <v>-1615700</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-1691500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1652700</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10679,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2091900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1778800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2079100</v>
       </c>
-      <c r="F100" s="3">
-        <v>-1338800</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>898200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2519900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2393500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1060800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>205000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1025800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3808200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>69900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1310300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6069600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2888700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3331800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1663700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2562800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3096100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>343900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-343900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2338900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-275000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>990500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-764700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3801100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4172300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3041000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-517600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-260200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>613600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2653900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-977200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3897800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-769700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1257800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>168300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-451900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>523500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="E101" s="3">
         <v>131500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-99300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>31100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>17300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-96200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>42300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>18600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-34800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-145300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>71600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>73200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>78900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>86000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>9800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>32500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>18300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>23300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>38100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-55900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-24900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>26900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>13200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-30300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-15700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-50500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-12300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>21100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-412400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-623500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-252300</v>
       </c>
-      <c r="F102" s="3">
-        <v>23500</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>1041900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1225800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-951400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1520400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1514700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>698600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1951700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1387600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-38000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-832900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>608400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2903100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5664600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1577400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2529600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>324800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1004000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2878500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>365300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>581500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2566900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5323400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7498200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-354100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-700000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4039600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3213100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>84500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1798500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2719700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1036700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-824700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-234500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>671400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-352100</v>
       </c>
     </row>
